--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T08:14:38+00:00</t>
+    <t>2023-08-18T14:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T14:55:17+00:00</t>
+    <t>2023-08-18T15:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T15:31:13+00:00</t>
+    <t>2023-08-21T08:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T08:03:13+00:00</t>
+    <t>2023-08-21T13:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T13:51:58+00:00</t>
+    <t>2023-08-21T14:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T14:32:39+00:00</t>
+    <t>2023-08-23T11:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -1750,13 +1754,13 @@
         <v>38</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AM1" t="s" s="2">
         <v>38</v>
@@ -1770,10 +1774,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1784,7 +1788,7 @@
         <v>36</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>38</v>
@@ -1793,19 +1797,19 @@
         <v>38</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1855,13 +1859,13 @@
         <v>38</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>38</v>
@@ -1887,10 +1891,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1901,7 +1905,7 @@
         <v>36</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>38</v>
@@ -1910,16 +1914,16 @@
         <v>38</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1970,22 +1974,22 @@
         <v>38</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>38</v>
@@ -2002,10 +2006,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2016,28 +2020,28 @@
         <v>36</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -2087,22 +2091,22 @@
         <v>38</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>38</v>
@@ -2119,10 +2123,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2133,7 +2137,7 @@
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>38</v>
@@ -2145,16 +2149,16 @@
         <v>38</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2180,13 +2184,13 @@
         <v>38</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>38</v>
@@ -2204,22 +2208,22 @@
         <v>38</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>38</v>
@@ -2236,21 +2240,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>38</v>
@@ -2262,16 +2266,16 @@
         <v>38</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2321,22 +2325,22 @@
         <v>38</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>38</v>
@@ -2353,14 +2357,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2379,16 +2383,16 @@
         <v>38</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2438,7 +2442,7 @@
         <v>38</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
@@ -2453,7 +2457,7 @@
         <v>38</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>38</v>
@@ -2470,14 +2474,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2496,16 +2500,16 @@
         <v>38</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2543,19 +2547,19 @@
         <v>38</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
@@ -2564,13 +2568,13 @@
         <v>37</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>38</v>
@@ -2587,13 +2591,13 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>38</v>
@@ -2603,10 +2607,10 @@
         <v>36</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>38</v>
@@ -2615,13 +2619,13 @@
         <v>38</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2672,7 +2676,7 @@
         <v>38</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2681,10 +2685,10 @@
         <v>37</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>38</v>
@@ -2704,14 +2708,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2724,25 +2728,25 @@
         <v>38</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>38</v>
@@ -2779,19 +2783,19 @@
         <v>38</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2800,13 +2804,13 @@
         <v>37</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>38</v>
@@ -2823,10 +2827,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2834,7 +2838,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>37</v>
@@ -2846,20 +2850,20 @@
         <v>38</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>38</v>
@@ -2896,19 +2900,19 @@
         <v>38</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
@@ -2917,22 +2921,22 @@
         <v>37</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>38</v>
@@ -2940,45 +2944,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>38</v>
@@ -3027,7 +3031,7 @@
         <v>38</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3036,22 +3040,22 @@
         <v>37</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>38</v>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3073,7 +3077,7 @@
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>38</v>
@@ -3085,13 +3089,13 @@
         <v>38</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3142,13 +3146,13 @@
         <v>38</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>38</v>
@@ -3157,7 +3161,7 @@
         <v>38</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>38</v>
@@ -3174,14 +3178,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3200,16 +3204,16 @@
         <v>38</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3247,19 +3251,19 @@
         <v>38</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -3268,13 +3272,13 @@
         <v>37</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>38</v>
@@ -3291,10 +3295,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3305,31 +3309,31 @@
         <v>36</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>38</v>
@@ -3354,13 +3358,13 @@
         <v>38</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>38</v>
@@ -3378,22 +3382,22 @@
         <v>38</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>38</v>
@@ -3402,7 +3406,7 @@
         <v>38</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>38</v>
@@ -3410,10 +3414,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3424,7 +3428,7 @@
         <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>38</v>
@@ -3433,22 +3437,22 @@
         <v>38</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>38</v>
@@ -3473,13 +3477,13 @@
         <v>38</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>38</v>
@@ -3497,22 +3501,22 @@
         <v>38</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>38</v>
@@ -3521,7 +3525,7 @@
         <v>38</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>38</v>
@@ -3529,10 +3533,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3540,10 +3544,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>38</v>
@@ -3552,22 +3556,22 @@
         <v>38</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>38</v>
@@ -3577,10 +3581,10 @@
         <v>38</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>38</v>
@@ -3616,22 +3620,22 @@
         <v>38</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>38</v>
@@ -3640,7 +3644,7 @@
         <v>38</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>38</v>
@@ -3648,10 +3652,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3662,7 +3666,7 @@
         <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>38</v>
@@ -3671,19 +3675,19 @@
         <v>38</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3697,7 +3701,7 @@
         <v>38</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>38</v>
@@ -3733,22 +3737,22 @@
         <v>38</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>38</v>
@@ -3757,7 +3761,7 @@
         <v>38</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>38</v>
@@ -3765,10 +3769,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3779,7 +3783,7 @@
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>38</v>
@@ -3788,19 +3792,19 @@
         <v>38</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3850,22 +3854,22 @@
         <v>38</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>38</v>
@@ -3874,7 +3878,7 @@
         <v>38</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>38</v>
@@ -3882,10 +3886,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3896,7 +3900,7 @@
         <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>38</v>
@@ -3905,19 +3909,19 @@
         <v>38</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3967,22 +3971,22 @@
         <v>38</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>38</v>
@@ -3991,7 +3995,7 @@
         <v>38</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>38</v>
@@ -3999,10 +4003,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4013,103 +4017,103 @@
         <v>36</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH21" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>45</v>
-      </c>
       <c r="AI21" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>38</v>
@@ -4120,10 +4124,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4143,22 +4147,22 @@
         <v>38</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>38</v>
@@ -4207,7 +4211,7 @@
         <v>38</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4216,22 +4220,22 @@
         <v>37</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>38</v>
@@ -4239,10 +4243,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4262,22 +4266,22 @@
         <v>38</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>38</v>
@@ -4326,7 +4330,7 @@
         <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4335,22 +4339,22 @@
         <v>37</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>38</v>
@@ -4358,10 +4362,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4372,7 +4376,7 @@
         <v>36</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>38</v>
@@ -4381,22 +4385,22 @@
         <v>38</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>38</v>
@@ -4421,11 +4425,11 @@
         <v>38</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>38</v>
@@ -4443,31 +4447,31 @@
         <v>38</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>38</v>
@@ -4475,10 +4479,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4489,7 +4493,7 @@
         <v>36</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>38</v>
@@ -4498,22 +4502,22 @@
         <v>38</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>38</v>
@@ -4562,42 +4566,42 @@
         <v>38</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4608,31 +4612,31 @@
         <v>36</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>38</v>
@@ -4681,31 +4685,31 @@
         <v>38</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>38</v>
@@ -4713,10 +4717,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4736,22 +4740,22 @@
         <v>38</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>38</v>
@@ -4800,7 +4804,7 @@
         <v>38</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4809,22 +4813,22 @@
         <v>37</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>38</v>
@@ -4832,10 +4836,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4846,7 +4850,7 @@
         <v>36</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>38</v>
@@ -4858,19 +4862,19 @@
         <v>38</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>38</v>
@@ -4895,13 +4899,13 @@
         <v>38</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>38</v>
@@ -4919,31 +4923,31 @@
         <v>38</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>38</v>
@@ -4951,10 +4955,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4965,7 +4969,7 @@
         <v>36</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>38</v>
@@ -4977,19 +4981,19 @@
         <v>38</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>38</v>
@@ -5038,31 +5042,31 @@
         <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>38</v>
@@ -5070,10 +5074,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5096,19 +5100,19 @@
         <v>38</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>38</v>
@@ -5157,7 +5161,7 @@
         <v>38</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5166,22 +5170,22 @@
         <v>37</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>38</v>
@@ -5189,10 +5193,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5215,19 +5219,19 @@
         <v>38</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>38</v>
@@ -5276,7 +5280,7 @@
         <v>38</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5285,16 +5289,16 @@
         <v>37</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>38</v>
@@ -5308,10 +5312,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5322,7 +5326,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>38</v>
@@ -5334,13 +5338,13 @@
         <v>38</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5391,13 +5395,13 @@
         <v>38</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>38</v>
@@ -5406,7 +5410,7 @@
         <v>38</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>38</v>
@@ -5423,14 +5427,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5449,16 +5453,16 @@
         <v>38</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5496,19 +5500,19 @@
         <v>38</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5517,13 +5521,13 @@
         <v>37</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>38</v>
@@ -5540,14 +5544,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5560,25 +5564,25 @@
         <v>38</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>38</v>
@@ -5627,7 +5631,7 @@
         <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5636,13 +5640,13 @@
         <v>37</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>38</v>
@@ -5659,10 +5663,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5685,19 +5689,19 @@
         <v>38</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>38</v>
@@ -5722,13 +5726,13 @@
         <v>38</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>38</v>
@@ -5746,7 +5750,7 @@
         <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5755,22 +5759,22 @@
         <v>37</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>38</v>
@@ -5778,10 +5782,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5792,7 +5796,7 @@
         <v>36</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>38</v>
@@ -5804,19 +5808,19 @@
         <v>38</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>38</v>
@@ -5865,31 +5869,31 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>38</v>
@@ -5897,10 +5901,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5923,19 +5927,19 @@
         <v>38</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>38</v>
@@ -5984,7 +5988,7 @@
         <v>38</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5993,22 +5997,22 @@
         <v>37</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>38</v>
@@ -6016,10 +6020,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6030,7 +6034,7 @@
         <v>36</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>38</v>
@@ -6042,19 +6046,19 @@
         <v>38</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>38</v>
@@ -6103,31 +6107,31 @@
         <v>38</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>38</v>
@@ -6135,10 +6139,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6149,7 +6153,7 @@
         <v>36</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>38</v>
@@ -6161,19 +6165,19 @@
         <v>38</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>38</v>
@@ -6198,13 +6202,13 @@
         <v>38</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>38</v>
@@ -6222,31 +6226,31 @@
         <v>38</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>38</v>
@@ -6254,10 +6258,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6268,7 +6272,7 @@
         <v>36</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>38</v>
@@ -6280,19 +6284,19 @@
         <v>38</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>38</v>
@@ -6341,31 +6345,31 @@
         <v>38</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>38</v>
@@ -6373,10 +6377,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6387,7 +6391,7 @@
         <v>36</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>38</v>
@@ -6399,16 +6403,16 @@
         <v>38</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6458,31 +6462,31 @@
         <v>38</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>38</v>
@@ -6490,10 +6494,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6516,19 +6520,19 @@
         <v>38</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>38</v>
@@ -6577,7 +6581,7 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6586,16 +6590,16 @@
         <v>37</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>38</v>
@@ -6609,10 +6613,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6623,7 +6627,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>38</v>
@@ -6635,13 +6639,13 @@
         <v>38</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6692,13 +6696,13 @@
         <v>38</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>38</v>
@@ -6707,7 +6711,7 @@
         <v>38</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>38</v>
@@ -6724,14 +6728,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6750,16 +6754,16 @@
         <v>38</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6797,19 +6801,19 @@
         <v>38</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6818,13 +6822,13 @@
         <v>37</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>38</v>
@@ -6841,14 +6845,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6861,25 +6865,25 @@
         <v>38</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>38</v>
@@ -6928,7 +6932,7 @@
         <v>38</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -6937,13 +6941,13 @@
         <v>37</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>38</v>
@@ -6960,10 +6964,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6971,10 +6975,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>38</v>
@@ -6986,19 +6990,19 @@
         <v>38</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>38</v>
@@ -7023,13 +7027,13 @@
         <v>38</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>38</v>
@@ -7047,31 +7051,31 @@
         <v>38</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>38</v>
@@ -7079,10 +7083,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7093,7 +7097,7 @@
         <v>36</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>38</v>
@@ -7105,19 +7109,19 @@
         <v>38</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>38</v>
@@ -7166,31 +7170,31 @@
         <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>38</v>
@@ -7198,14 +7202,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7224,16 +7228,16 @@
         <v>38</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7283,7 +7287,7 @@
         <v>38</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7292,22 +7296,22 @@
         <v>37</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>38</v>
@@ -7315,10 +7319,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7329,7 +7333,7 @@
         <v>36</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>38</v>
@@ -7338,22 +7342,22 @@
         <v>38</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>38</v>
@@ -7402,25 +7406,25 @@
         <v>38</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>38</v>
@@ -7434,10 +7438,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7454,25 +7458,25 @@
         <v>38</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>38</v>
@@ -7521,7 +7525,7 @@
         <v>38</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7530,16 +7534,16 @@
         <v>37</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>38</v>
@@ -7553,10 +7557,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7567,7 +7571,7 @@
         <v>36</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>38</v>
@@ -7579,13 +7583,13 @@
         <v>38</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7636,13 +7640,13 @@
         <v>38</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>38</v>
@@ -7651,7 +7655,7 @@
         <v>38</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>38</v>
@@ -7668,14 +7672,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7694,16 +7698,16 @@
         <v>38</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7741,19 +7745,19 @@
         <v>38</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7762,13 +7766,13 @@
         <v>37</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>38</v>
@@ -7785,14 +7789,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7805,25 +7809,25 @@
         <v>38</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>38</v>
@@ -7872,7 +7876,7 @@
         <v>38</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7881,13 +7885,13 @@
         <v>37</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>38</v>
@@ -7904,10 +7908,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7915,10 +7919,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>38</v>
@@ -7927,19 +7931,19 @@
         <v>38</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7989,31 +7993,31 @@
         <v>38</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>38</v>
@@ -8021,10 +8025,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8032,10 +8036,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>38</v>
@@ -8044,19 +8048,19 @@
         <v>38</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8082,13 +8086,13 @@
         <v>38</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>38</v>
@@ -8106,25 +8110,25 @@
         <v>38</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>38</v>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-23T11:58:54+00:00</t>
+    <t>2023-08-24T06:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T06:27:04+00:00</t>
+    <t>2023-08-24T15:04:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T15:04:54+00:00</t>
+    <t>2023-08-25T12:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-25T12:58:54+00:00</t>
+    <t>2023-09-06T15:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T15:21:37+00:00</t>
+    <t>2023-09-06T15:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T15:44:31+00:00</t>
+    <t>2023-09-06T16:00:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T16:00:39+00:00</t>
+    <t>2023-09-06T16:25:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T16:25:28+00:00</t>
+    <t>2023-09-07T06:19:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T06:19:17+00:00</t>
+    <t>2023-09-07T10:24:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T10:24:14+00:00</t>
+    <t>2023-09-07T10:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
+++ b/ig/specifications_fonctionnelles/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T10:35:42+00:00</t>
+    <t>2023-09-11T10:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
